--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20221.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20221.xlsx
@@ -555,22 +555,22 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>41</v>
       </c>
       <c r="G5">
-        <v>97.62</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -649,16 +649,19 @@
         <v>40</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>40</v>
       </c>
-      <c r="E2">
-        <v>40</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -672,16 +675,19 @@
         <v>44</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>44</v>
       </c>
-      <c r="E3">
-        <v>44</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -695,16 +701,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>95.34999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -715,19 +724,22 @@
         <v>13</v>
       </c>
       <c r="C5">
+        <v>43</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>42</v>
       </c>
-      <c r="D5">
-        <v>42</v>
-      </c>
-      <c r="E5">
-        <v>42</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>97.67</v>
+      </c>
+      <c r="H5">
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -815,7 +827,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -841,7 +853,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -858,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -878,7 +890,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -887,13 +899,13 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5">
-        <v>97.62</v>
+        <v>97.67</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20221.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20221.xlsx
@@ -753,16 +753,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>95.23999999999999</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -922,16 +925,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>90.48</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20221.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20221.xlsx
@@ -830,7 +830,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -856,7 +856,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -873,16 +873,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4">
-        <v>95.34999999999999</v>
+        <v>97.67</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -934,7 +934,7 @@
         <v>95.23999999999999</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
